--- a/data/trans_dic/P2A_enfcro_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P2A_enfcro_R-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con enfermedades crónicas</t>
+          <t>Hogares con personas con enfermedades crónicas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>23,89; 44,22</t>
+          <t>23,86; 44,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>47,92; 77,45</t>
+          <t>49,07; 77,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38,51; 63,6</t>
+          <t>40,52; 63,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>93,61; 100,0</t>
+          <t>95,67; 100,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>22,22; 44,36</t>
+          <t>22,6; 44,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,79; 66,86</t>
+          <t>39,36; 67,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,52; 67,88</t>
+          <t>44,8; 68,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>96,76; 100,0</t>
+          <t>96,8; 100,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26,71; 41,81</t>
+          <t>25,66; 40,74</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47,34; 68,51</t>
+          <t>46,92; 67,91</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45,52; 62,42</t>
+          <t>45,79; 62,54</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,46; 100,0</t>
+          <t>97,12; 100,0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,45; 51,1</t>
+          <t>31,67; 50,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>32,83; 54,82</t>
+          <t>33,25; 54,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43,09; 63,83</t>
+          <t>45,36; 64,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>95,85; 100,0</t>
+          <t>96,18; 100,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>39,16; 59,39</t>
+          <t>39,7; 59,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,71; 54,51</t>
+          <t>34,3; 54,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,22; 54,39</t>
+          <t>36,08; 54,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>87,0; 96,5</t>
+          <t>87,4; 96,55</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>37,64; 51,1</t>
+          <t>36,6; 51,05</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36,4; 51,28</t>
+          <t>36,94; 51,44</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42,77; 56,38</t>
+          <t>42,82; 56,43</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>93,17; 98,07</t>
+          <t>93,07; 98,07</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>28,43; 49,15</t>
+          <t>28,26; 48,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37,54; 60,89</t>
+          <t>38,99; 62,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26,65; 49,35</t>
+          <t>28,86; 49,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>89,36; 98,77</t>
+          <t>89,45; 98,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>25,27; 43,16</t>
+          <t>25,31; 43,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34,89; 55,09</t>
+          <t>34,43; 55,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,2; 49,3</t>
+          <t>29,22; 48,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>94,49; 100,0</t>
+          <t>94,53; 100,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29,58; 42,98</t>
+          <t>29,58; 42,92</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>39,08; 55,39</t>
+          <t>39,28; 55,3</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31,37; 46,21</t>
+          <t>31,17; 45,48</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>94,1; 98,99</t>
+          <t>94,02; 98,97</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>37,54; 56,91</t>
+          <t>36,85; 56,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36,29; 60,21</t>
+          <t>35,45; 59,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>44,07; 70,01</t>
+          <t>44,65; 70,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>87,4; 98,19</t>
+          <t>88,08; 98,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>42,2; 61,1</t>
+          <t>41,77; 60,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,68; 61,77</t>
+          <t>38,63; 61,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,57; 63,49</t>
+          <t>38,68; 63,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>85,86; 98,53</t>
+          <t>84,33; 98,42</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>43,24; 56,49</t>
+          <t>42,79; 56,47</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>40,92; 57,76</t>
+          <t>40,93; 56,94</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45,42; 63,16</t>
+          <t>45,9; 63,19</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>89,42; 97,68</t>
+          <t>89,12; 97,4</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>37,21; 86,77</t>
+          <t>36,55; 86,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>33,76; 74,71</t>
+          <t>34,23; 74,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32,88; 60,24</t>
+          <t>31,33; 59,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>97,23; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,08; 58,99</t>
+          <t>12,5; 60,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,09; 68,21</t>
+          <t>33,22; 66,95</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,39; 53,52</t>
+          <t>27,87; 53,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>78,64; 100,0</t>
+          <t>81,67; 100,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>30,77; 64,63</t>
+          <t>27,85; 63,88</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39,27; 66,08</t>
+          <t>40,01; 66,26</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33,09; 53,05</t>
+          <t>34,0; 53,83</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>88,0; 100,0</t>
+          <t>87,42; 100,0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>25,33; 48,29</t>
+          <t>26,0; 48,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>39,44; 64,78</t>
+          <t>41,05; 64,98</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26,04; 56,47</t>
+          <t>25,16; 56,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>83,87; 96,75</t>
+          <t>83,71; 97,14</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>31,17; 52,32</t>
+          <t>31,73; 53,5</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>46,95; 70,49</t>
+          <t>46,68; 69,71</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,12; 46,33</t>
+          <t>18,7; 48,16</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>88,8; 98,09</t>
+          <t>89,7; 98,25</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>31,85; 47,74</t>
+          <t>31,99; 46,96</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>47,31; 64,64</t>
+          <t>47,52; 64,61</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>25,74; 46,78</t>
+          <t>24,9; 45,99</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>88,82; 96,87</t>
+          <t>89,38; 96,64</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>29,26; 43,99</t>
+          <t>28,86; 43,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>46,67; 61,78</t>
+          <t>46,12; 61,97</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23,78; 37,68</t>
+          <t>24,42; 38,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>91,59; 97,82</t>
+          <t>90,63; 97,74</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>33,87; 49,96</t>
+          <t>34,32; 49,82</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,67; 62,02</t>
+          <t>46,23; 61,91</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,88; 41,32</t>
+          <t>27,4; 41,63</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>91,43; 97,83</t>
+          <t>91,74; 97,87</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>33,59; 44,23</t>
+          <t>33,51; 44,35</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>48,28; 59,32</t>
+          <t>48,71; 59,64</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27,43; 37,49</t>
+          <t>27,82; 37,61</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>92,64; 97,29</t>
+          <t>92,82; 97,28</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>33,91; 50,28</t>
+          <t>34,4; 50,78</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>24,44; 37,87</t>
+          <t>24,69; 38,49</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32,21; 45,41</t>
+          <t>31,47; 45,06</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>83,1; 92,84</t>
+          <t>82,33; 92,69</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>37,58; 54,43</t>
+          <t>38,68; 53,82</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>31,78; 46,23</t>
+          <t>31,74; 45,89</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,66; 45,77</t>
+          <t>32,47; 45,79</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>86,66; 94,98</t>
+          <t>86,62; 94,98</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>38,33; 50,11</t>
+          <t>38,24; 50,05</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30,12; 39,89</t>
+          <t>30,47; 40,21</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34,17; 43,63</t>
+          <t>34,08; 43,03</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>86,85; 92,98</t>
+          <t>86,99; 92,97</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>36,09; 43,32</t>
+          <t>36,33; 43,1</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>43,08; 50,23</t>
+          <t>43,1; 50,27</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>38,94; 45,67</t>
+          <t>39,05; 46,81</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>93,52; 96,48</t>
+          <t>93,65; 96,55</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>39,43; 46,47</t>
+          <t>39,46; 46,14</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>44,3; 51,32</t>
+          <t>44,4; 51,25</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>37,88; 44,67</t>
+          <t>37,91; 44,56</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>93,08; 96,1</t>
+          <t>92,96; 96,1</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>38,83; 43,63</t>
+          <t>38,91; 43,8</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>44,8; 49,78</t>
+          <t>44,72; 50,14</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>39,31; 44,27</t>
+          <t>39,18; 44,09</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>93,84; 95,9</t>
+          <t>93,79; 95,86</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hogares con personas con enfermedades crónicas (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>15957</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>16257</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>23578</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>72563</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>16978</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>20530</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>29051</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>78882</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>32935</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>36788</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>52629</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>151445</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>11384; 21266</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>12444; 19585</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>18392; 28913</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>70112; 73282</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>11566; 22639</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>14989; 25587</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>23293; 35576</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>76828; 79366</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>25372; 40281</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>29766; 43081</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>44595; 60905</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>148255; 152648</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>27413</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>23768</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>38653</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>126413</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>31469</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>26189</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>36535</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>119098</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>58882</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>49957</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>75187</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>245511</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>21501; 34358</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>18081; 29700</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>32069; 45529</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>122778; 127654</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>25779; 38714</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>20196; 31800</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>28863; 43941</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>111525; 123190</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>48612; 67804</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>41845; 58268</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>64523; 85042</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>237554; 250335</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>24690</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>26095</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>22271</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>55688</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>23121</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>27006</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>25229</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>66484</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>47811</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>53100</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>47499</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>122172</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>18281; 31123</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>20550; 32698</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>16769; 28831</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>52121; 57611</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>17187; 29831</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>20635; 33485</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>19335; 32319</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>63489; 67163</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>39219; 56906</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>44251; 62297</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>38740; 56528</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>117926; 124133</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>31220</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>24041</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>26377</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>66706</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>38253</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>27715</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>24368</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>73584</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>69472</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>51756</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>50745</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>140292</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>24343; 37588</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>17611; 29585</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>20144; 31908</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>61781; 68863</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>30711; 44389</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>21429; 34259</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>18429; 30170</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>65890; 76902</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>59727; 78813</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>43041; 59869</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>42575; 58621</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>132147; 144420</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>6251</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>9834</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>15109</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>34513</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>3727</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>12547</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>14229</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>38455</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>9979</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>22381</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>29338</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>72968</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>3488; 8294</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>6176; 13371</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>10143; 19263</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1425; 6883</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>8182; 16489</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>9899; 19086</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>33253; 40719</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>5831; 13378</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>17071; 28274</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>23082; 36545</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>65767; 75232</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>16892</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>23454</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>10976</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>42493</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>22221</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>29223</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>9922</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>53306</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>39113</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>52677</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>20897</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>95798</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>12129; 22562</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>18286; 28943</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>6863; 15349</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>38647; 44845</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>16587; 27965</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>23121; 34527</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>5863; 15100</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>50401; 55205</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>31650; 46452</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>44703; 60778</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>14600; 26970</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>91483; 98918</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>39978</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>62810</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>36141</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>118612</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>46000</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>65966</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>40750</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>148939</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>85978</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>128775</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>76891</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>267551</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>31929; 47998</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>53819; 72324</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>28515; 44462</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>112847; 121689</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>38026; 55194</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>56295; 75396</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>32635; 49591</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>143131; 152681</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>74194; 98201</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>116158; 142235</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>65615; 88720</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>260379; 272902</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>37744</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>36135</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>49569</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>116678</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>44463</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>49897</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>54536</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>143420</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>82208</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>86032</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>104105</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>260097</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>31021; 45784</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>28523; 44470</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>40803; 58416</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>108367; 121997</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>37356; 51979</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>41407; 59872</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>45208; 63752</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>135818; 148931</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>71409; 93465</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>74959; 98930</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>91635; 115686</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>250886; 268150</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>893</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>925</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>671</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>1818</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>200145</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>222394</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>222674</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>633667</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>226233</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>259073</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>234618</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>722169</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>426378</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>481467</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>457292</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>1355836</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>182877; 216941</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>205564; 239769</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>205187; 245939</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>623857; 643158</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>208567; 243856</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>239227; 276099</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>216460; 254440</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>708305; 732249</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>401501; 451997</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>454290; 509320</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>429534; 483422</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>1339500; 1368932</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/P2A_enfcro_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P2A_enfcro_R-Provincia-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>23,86; 44,58</t>
+          <t>23,29; 44,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>49,07; 77,24</t>
+          <t>48,68; 76,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40,52; 63,71</t>
+          <t>39,65; 63,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>95,67; 100,0</t>
+          <t>94,96; 100,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>22,6; 44,25</t>
+          <t>23,8; 44,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,36; 67,19</t>
+          <t>40,5; 66,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,8; 68,42</t>
+          <t>44,73; 66,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>96,8; 100,0</t>
+          <t>96,83; 100,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>25,66; 40,74</t>
+          <t>26,1; 41,78</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46,92; 67,91</t>
+          <t>47,7; 67,52</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45,79; 62,54</t>
+          <t>45,84; 62,94</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,12; 100,0</t>
+          <t>96,83; 100,0</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,67; 50,61</t>
+          <t>30,91; 50,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>33,25; 54,61</t>
+          <t>32,6; 54,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45,36; 64,4</t>
+          <t>44,64; 64,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>96,18; 100,0</t>
+          <t>96,25; 100,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>39,7; 59,62</t>
+          <t>38,02; 57,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,3; 54,0</t>
+          <t>33,95; 54,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,08; 54,93</t>
+          <t>36,88; 54,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>87,4; 96,55</t>
+          <t>87,31; 96,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>36,6; 51,05</t>
+          <t>37,34; 52,21</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36,94; 51,44</t>
+          <t>35,82; 51,52</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42,82; 56,43</t>
+          <t>43,85; 56,49</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>93,07; 98,07</t>
+          <t>93,23; 97,99</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>28,26; 48,11</t>
+          <t>27,96; 48,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>38,99; 62,03</t>
+          <t>38,15; 61,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28,86; 49,61</t>
+          <t>27,78; 49,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>89,45; 98,87</t>
+          <t>90,13; 98,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>25,31; 43,93</t>
+          <t>25,29; 43,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34,43; 55,87</t>
+          <t>35,76; 56,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,22; 48,84</t>
+          <t>28,48; 47,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>94,53; 100,0</t>
+          <t>94,47; 100,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29,58; 42,92</t>
+          <t>29,49; 42,94</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>39,28; 55,3</t>
+          <t>38,81; 55,08</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31,17; 45,48</t>
+          <t>30,33; 45,71</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>94,02; 98,97</t>
+          <t>94,31; 99,03</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>36,85; 56,9</t>
+          <t>37,51; 56,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>35,45; 59,55</t>
+          <t>36,56; 60,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>44,65; 70,73</t>
+          <t>45,6; 69,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>88,08; 98,18</t>
+          <t>88,04; 98,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>41,77; 60,38</t>
+          <t>42,25; 61,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,63; 61,76</t>
+          <t>37,48; 61,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,68; 63,32</t>
+          <t>38,67; 64,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>84,33; 98,42</t>
+          <t>84,58; 98,22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>42,79; 56,47</t>
+          <t>43,32; 56,49</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>40,93; 56,94</t>
+          <t>41,02; 58,95</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45,9; 63,19</t>
+          <t>45,6; 63,11</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>89,12; 97,4</t>
+          <t>89,6; 97,5</t>
         </is>
       </c>
     </row>
@@ -1277,17 +1277,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>36,55; 86,93</t>
+          <t>37,46; 87,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>34,23; 74,11</t>
+          <t>34,36; 74,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31,33; 59,5</t>
+          <t>34,08; 61,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1297,42 +1297,42 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,5; 60,38</t>
+          <t>12,71; 63,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,22; 66,95</t>
+          <t>32,32; 66,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,87; 53,74</t>
+          <t>27,49; 54,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>81,67; 100,0</t>
+          <t>80,4; 100,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>27,85; 63,88</t>
+          <t>28,55; 65,43</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40,01; 66,26</t>
+          <t>38,19; 64,9</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34,0; 53,83</t>
+          <t>33,66; 53,29</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>87,42; 100,0</t>
+          <t>89,02; 100,0</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>26,0; 48,36</t>
+          <t>24,43; 47,99</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>41,05; 64,98</t>
+          <t>39,28; 65,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25,16; 56,26</t>
+          <t>26,89; 57,29</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>83,71; 97,14</t>
+          <t>83,9; 97,03</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>31,73; 53,5</t>
+          <t>32,38; 52,61</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>46,68; 69,71</t>
+          <t>47,02; 70,72</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,7; 48,16</t>
+          <t>19,19; 48,17</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>89,7; 98,25</t>
+          <t>88,78; 98,06</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>31,99; 46,96</t>
+          <t>31,74; 47,28</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>47,52; 64,61</t>
+          <t>47,71; 64,22</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24,9; 45,99</t>
+          <t>26,73; 46,62</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>89,38; 96,64</t>
+          <t>88,63; 96,58</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>28,86; 43,38</t>
+          <t>29,14; 44,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>46,12; 61,97</t>
+          <t>45,93; 61,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24,42; 38,08</t>
+          <t>24,2; 38,69</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>90,63; 97,74</t>
+          <t>91,56; 97,67</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>34,32; 49,82</t>
+          <t>34,5; 48,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,23; 61,91</t>
+          <t>46,74; 61,81</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,4; 41,63</t>
+          <t>27,31; 42,68</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>91,74; 97,87</t>
+          <t>91,82; 98,1</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>33,51; 44,35</t>
+          <t>33,62; 44,11</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>48,71; 59,64</t>
+          <t>48,28; 59,0</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27,82; 37,61</t>
+          <t>27,81; 37,62</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>92,82; 97,28</t>
+          <t>92,74; 97,28</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>34,4; 50,78</t>
+          <t>34,13; 50,17</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>24,69; 38,49</t>
+          <t>24,78; 38,84</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>31,47; 45,06</t>
+          <t>31,72; 44,82</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>82,33; 92,69</t>
+          <t>82,79; 92,93</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>38,68; 53,82</t>
+          <t>38,52; 54,09</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>31,74; 45,89</t>
+          <t>31,55; 45,25</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,47; 45,79</t>
+          <t>33,46; 46,76</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>86,62; 94,98</t>
+          <t>86,82; 94,67</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>38,24; 50,05</t>
+          <t>38,36; 49,87</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30,47; 40,21</t>
+          <t>30,28; 40,04</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34,08; 43,03</t>
+          <t>34,61; 43,66</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>86,99; 92,97</t>
+          <t>86,33; 92,78</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>36,33; 43,1</t>
+          <t>35,99; 43,11</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>43,1; 50,27</t>
+          <t>42,91; 50,31</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>39,05; 46,81</t>
+          <t>39,25; 45,89</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>93,65; 96,55</t>
+          <t>93,73; 96,48</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>39,46; 46,14</t>
+          <t>39,5; 46,38</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>44,4; 51,25</t>
+          <t>44,59; 51,65</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>37,91; 44,56</t>
+          <t>37,51; 44,38</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>92,96; 96,1</t>
+          <t>93,06; 96,13</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>38,91; 43,8</t>
+          <t>38,72; 43,93</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>44,72; 50,14</t>
+          <t>44,74; 49,91</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>39,18; 44,09</t>
+          <t>39,26; 44,1</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>93,79; 95,86</t>
+          <t>93,84; 95,98</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11384; 21266</t>
+          <t>11112; 21441</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12444; 19585</t>
+          <t>12344; 19457</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18392; 28913</t>
+          <t>17995; 28700</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>70112; 73282</t>
+          <t>69592; 73282</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>11566; 22639</t>
+          <t>12176; 22974</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14989; 25587</t>
+          <t>15421; 25320</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23293; 35576</t>
+          <t>23259; 34806</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>76828; 79366</t>
+          <t>76848; 79366</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>25372; 40281</t>
+          <t>25806; 41313</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29766; 43081</t>
+          <t>30258; 42831</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>44595; 60905</t>
+          <t>44640; 61295</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>148255; 152648</t>
+          <t>147814; 152648</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21501; 34358</t>
+          <t>20981; 33962</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18081; 29700</t>
+          <t>17730; 29659</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32069; 45529</t>
+          <t>31559; 45867</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>122778; 127654</t>
+          <t>122864; 127654</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>25779; 38714</t>
+          <t>24687; 37235</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20196; 31800</t>
+          <t>19989; 32299</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28863; 43941</t>
+          <t>29500; 43971</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>111525; 123190</t>
+          <t>111407; 123332</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>48612; 67804</t>
+          <t>49590; 69347</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>41845; 58268</t>
+          <t>40575; 58354</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>64523; 85042</t>
+          <t>66081; 85126</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>237554; 250335</t>
+          <t>237958; 250132</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18281; 31123</t>
+          <t>18091; 31524</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20550; 32698</t>
+          <t>20108; 32196</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16769; 28831</t>
+          <t>16142; 28831</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>52121; 57611</t>
+          <t>52519; 57625</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>17187; 29831</t>
+          <t>17172; 29759</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20635; 33485</t>
+          <t>21432; 33598</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19335; 32319</t>
+          <t>18847; 31400</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>63489; 67163</t>
+          <t>63450; 67163</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>39219; 56906</t>
+          <t>39110; 56934</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>44251; 62297</t>
+          <t>43719; 62046</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>38740; 56528</t>
+          <t>37699; 56814</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>117926; 124133</t>
+          <t>118298; 124216</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>24343; 37588</t>
+          <t>24778; 37314</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17611; 29585</t>
+          <t>18162; 30085</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20144; 31908</t>
+          <t>20569; 31500</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>61781; 68863</t>
+          <t>61753; 68881</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>30711; 44389</t>
+          <t>31062; 45179</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21429; 34259</t>
+          <t>20790; 34112</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18429; 30170</t>
+          <t>18427; 30627</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>65890; 76902</t>
+          <t>66085; 76740</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>59727; 78813</t>
+          <t>60455; 78841</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>43041; 59869</t>
+          <t>43129; 61985</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>42575; 58621</t>
+          <t>42300; 58539</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>132147; 144420</t>
+          <t>132856; 144578</t>
         </is>
       </c>
     </row>
@@ -3041,17 +3041,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3488; 8294</t>
+          <t>3574; 8302</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6176; 13371</t>
+          <t>6199; 13511</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10143; 19263</t>
+          <t>11033; 19837</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -3061,42 +3061,42 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1425; 6883</t>
+          <t>1449; 7240</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8182; 16489</t>
+          <t>7960; 16484</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9899; 19086</t>
+          <t>9763; 19360</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>33253; 40719</t>
+          <t>32739; 40719</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5831; 13378</t>
+          <t>5980; 13701</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17071; 28274</t>
+          <t>16298; 27697</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>23082; 36545</t>
+          <t>22853; 36181</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>65767; 75232</t>
+          <t>66971; 75232</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>12129; 22562</t>
+          <t>11398; 22390</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>18286; 28943</t>
+          <t>17496; 29002</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6863; 15349</t>
+          <t>7337; 15631</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>38647; 44845</t>
+          <t>38736; 44794</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>16587; 27965</t>
+          <t>16926; 27500</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23121; 34527</t>
+          <t>23292; 35030</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5863; 15100</t>
+          <t>6017; 15103</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>50401; 55205</t>
+          <t>49882; 55097</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>31650; 46452</t>
+          <t>31405; 46776</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>44703; 60778</t>
+          <t>44884; 60414</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14600; 26970</t>
+          <t>15674; 27338</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>91483; 98918</t>
+          <t>90719; 98850</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>31929; 47998</t>
+          <t>32248; 48809</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>53819; 72324</t>
+          <t>53599; 71839</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>28515; 44462</t>
+          <t>28257; 45175</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>112847; 121689</t>
+          <t>113999; 121610</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>38026; 55194</t>
+          <t>38220; 53763</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>56295; 75396</t>
+          <t>56918; 75271</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>32635; 49591</t>
+          <t>32538; 50844</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>143131; 152681</t>
+          <t>143244; 153043</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>74194; 98201</t>
+          <t>74439; 97666</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>116158; 142235</t>
+          <t>115138; 140695</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>65615; 88720</t>
+          <t>65596; 88743</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>260379; 272902</t>
+          <t>260160; 272901</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>31021; 45784</t>
+          <t>30775; 45239</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>28523; 44470</t>
+          <t>28628; 44874</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>40803; 58416</t>
+          <t>41132; 58115</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>108367; 121997</t>
+          <t>108963; 122317</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>37356; 51979</t>
+          <t>37200; 52240</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>41407; 59872</t>
+          <t>41164; 59033</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>45208; 63752</t>
+          <t>46587; 65097</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>135818; 148931</t>
+          <t>136125; 148443</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>71409; 93465</t>
+          <t>71628; 93125</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>74959; 98930</t>
+          <t>74482; 98492</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>91635; 115686</t>
+          <t>93057; 117378</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>250886; 268150</t>
+          <t>249002; 267589</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>182877; 216941</t>
+          <t>181145; 217000</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>205564; 239769</t>
+          <t>204644; 239956</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>205187; 245939</t>
+          <t>206228; 241106</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>623857; 643158</t>
+          <t>624388; 642736</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>208567; 243856</t>
+          <t>208778; 245146</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>239227; 276099</t>
+          <t>240217; 278303</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>216460; 254440</t>
+          <t>214222; 253416</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>708305; 732249</t>
+          <t>709120; 732502</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>401501; 451997</t>
+          <t>399580; 453282</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>454290; 509320</t>
+          <t>454476; 506927</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>429534; 483422</t>
+          <t>430455; 483498</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1339500; 1368932</t>
+          <t>1340125; 1370764</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_enfcro_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P2A_enfcro_R-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>33,18%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>53,91%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>55,87%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>99,34%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>33,45%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>64,11%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>51,95%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>99,02%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>33,18%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>53,91%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>55,87%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>23,29; 44,94</t>
+          <t>22,22; 44,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>48,68; 76,73</t>
+          <t>39,79; 66,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39,65; 63,24</t>
+          <t>43,52; 67,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>94,96; 100,0</t>
+          <t>96,55; 100,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,8; 44,9</t>
+          <t>23,89; 44,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,5; 66,49</t>
+          <t>47,92; 77,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,73; 66,94</t>
+          <t>38,51; 63,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>96,83; 100,0</t>
+          <t>92,81; 100,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26,1; 41,78</t>
+          <t>26,71; 41,81</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47,7; 67,52</t>
+          <t>47,34; 68,51</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45,84; 62,94</t>
+          <t>45,52; 62,42</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,83; 100,0</t>
+          <t>97,01; 100,0</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>48,46%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>44,47%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>45,67%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>93,67%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>40,38%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>43,7%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>54,67%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>99,03%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>48,46%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>44,47%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>45,67%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,06%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>30,91; 50,03</t>
+          <t>39,16; 59,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>32,6; 54,53</t>
+          <t>34,71; 54,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44,64; 64,87</t>
+          <t>37,22; 54,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>96,25; 100,0</t>
+          <t>87,32; 96,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>38,02; 57,34</t>
+          <t>31,45; 51,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,95; 54,85</t>
+          <t>32,83; 54,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,88; 54,97</t>
+          <t>43,09; 63,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>87,31; 96,66</t>
+          <t>95,37; 100,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>37,34; 52,21</t>
+          <t>37,64; 51,1</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35,82; 51,52</t>
+          <t>36,4; 51,28</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43,85; 56,49</t>
+          <t>42,77; 56,38</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>93,23; 97,99</t>
+          <t>93,05; 98,03</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>34,05%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>45,06%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>38,12%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>98,95%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>38,16%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>49,5%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>38,32%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>95,57%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>34,05%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>45,06%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>38,12%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,26%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>27,96; 48,73</t>
+          <t>25,27; 43,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>38,15; 61,08</t>
+          <t>34,89; 55,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27,78; 49,61</t>
+          <t>29,2; 49,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>90,13; 98,9</t>
+          <t>94,16; 100,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>25,29; 43,83</t>
+          <t>28,43; 49,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,76; 56,06</t>
+          <t>37,54; 60,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,48; 47,45</t>
+          <t>26,65; 49,35</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>94,47; 100,0</t>
+          <t>89,25; 98,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29,49; 42,94</t>
+          <t>29,58; 42,98</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>38,81; 55,08</t>
+          <t>39,08; 55,39</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30,33; 45,71</t>
+          <t>31,37; 46,21</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>94,31; 99,03</t>
+          <t>93,85; 98,93</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>52,03%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>49,96%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>51,14%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>94,41%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>47,26%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>48,39%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>58,47%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>95,1%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>52,03%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>49,96%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>51,14%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>95,0%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>37,51; 56,49</t>
+          <t>42,2; 61,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36,56; 60,56</t>
+          <t>37,68; 61,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45,6; 69,82</t>
+          <t>38,57; 63,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>88,04; 98,2</t>
+          <t>85,02; 98,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>42,25; 61,45</t>
+          <t>37,54; 56,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,48; 61,49</t>
+          <t>36,29; 60,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,67; 64,28</t>
+          <t>44,07; 70,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>84,58; 98,22</t>
+          <t>88,46; 98,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>43,32; 56,49</t>
+          <t>43,24; 56,49</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>41,02; 58,95</t>
+          <t>40,92; 57,76</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45,6; 63,11</t>
+          <t>45,42; 63,16</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>89,6; 97,5</t>
+          <t>89,83; 97,87</t>
         </is>
       </c>
     </row>
@@ -1209,44 +1209,44 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>32,7%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>50,94%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>40,06%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>96,71%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>65,52%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>54,5%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>46,67%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>32,7%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>50,94%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>40,06%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>94,44%</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
           <t>47,65%</t>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>37,46; 87,01</t>
+          <t>12,08; 58,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>34,36; 74,88</t>
+          <t>34,09; 68,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34,08; 61,27</t>
+          <t>28,39; 53,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
+          <t>89,01; 100,0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>37,21; 86,77</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>33,76; 74,71</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>32,88; 60,24</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>12,71; 63,51</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>32,32; 66,93</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>27,49; 54,51</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>80,4; 100,0</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>28,55; 65,43</t>
+          <t>30,77; 64,63</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38,19; 64,9</t>
+          <t>39,27; 66,08</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33,66; 53,29</t>
+          <t>33,09; 53,05</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>89,02; 100,0</t>
+          <t>93,82; 100,0</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>42,51%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>59,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>31,64%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>94,52%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>36,2%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>52,66%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>40,23%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>92,04%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>42,51%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>59,0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>31,64%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,79%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>24,43; 47,99</t>
+          <t>31,17; 52,32</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>39,28; 65,11</t>
+          <t>46,95; 70,49</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26,89; 57,29</t>
+          <t>18,12; 46,33</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>83,9; 97,03</t>
+          <t>88,28; 98,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>32,38; 52,61</t>
+          <t>25,33; 48,29</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>47,02; 70,72</t>
+          <t>39,44; 64,78</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19,19; 48,17</t>
+          <t>26,04; 56,47</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>88,78; 98,06</t>
+          <t>84,08; 97,18</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>31,74; 47,28</t>
+          <t>31,85; 47,74</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>47,71; 64,22</t>
+          <t>47,31; 64,64</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>26,73; 46,62</t>
+          <t>25,74; 46,78</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>88,63; 96,58</t>
+          <t>89,23; 96,87</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>41,52%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>54,17%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>34,21%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>95,07%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>36,13%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>53,82%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>30,95%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>95,26%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>41,52%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>54,17%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>34,21%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,03%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>29,14; 44,11</t>
+          <t>33,87; 49,96</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>45,93; 61,56</t>
+          <t>46,67; 62,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24,2; 38,69</t>
+          <t>26,88; 41,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>91,56; 97,67</t>
+          <t>90,41; 97,57</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>34,5; 48,53</t>
+          <t>29,26; 43,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,74; 61,81</t>
+          <t>46,67; 61,78</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,31; 42,68</t>
+          <t>23,78; 37,68</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>91,82; 98,1</t>
+          <t>90,99; 97,67</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>33,62; 44,11</t>
+          <t>33,59; 44,23</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>48,28; 59,0</t>
+          <t>48,28; 59,32</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27,81; 37,62</t>
+          <t>27,43; 37,49</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>92,74; 97,28</t>
+          <t>92,03; 96,95</t>
         </is>
       </c>
     </row>
@@ -1629,42 +1629,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>46,04%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>38,24%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>39,17%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>91,68%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>41,86%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>31,28%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>38,23%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>88,65%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>46,04%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>38,24%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>39,17%</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,47%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>34,13; 50,17</t>
+          <t>37,58; 54,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>24,78; 38,84</t>
+          <t>31,78; 46,23</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>31,72; 44,82</t>
+          <t>32,66; 45,77</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>82,79; 92,93</t>
+          <t>86,88; 95,19</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>38,52; 54,09</t>
+          <t>33,91; 50,28</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>31,55; 45,25</t>
+          <t>24,44; 37,87</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,46; 46,76</t>
+          <t>32,21; 45,41</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>86,82; 94,67</t>
+          <t>83,63; 93,11</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>38,36; 49,87</t>
+          <t>38,33; 50,11</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30,28; 40,04</t>
+          <t>30,12; 39,89</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34,61; 43,66</t>
+          <t>34,17; 43,63</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>86,33; 92,78</t>
+          <t>87,1; 93,26</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>42,8%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>48,08%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>41,09%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>94,77%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>39,76%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>46,63%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>42,38%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>95,12%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>42,8%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>48,08%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>41,09%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,83%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>35,99; 43,11</t>
+          <t>39,43; 46,47</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>42,91; 50,31</t>
+          <t>44,3; 51,32</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>39,25; 45,89</t>
+          <t>37,88; 44,67</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>93,73; 96,48</t>
+          <t>93,03; 96,1</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>39,5; 46,38</t>
+          <t>36,09; 43,32</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>44,59; 51,65</t>
+          <t>43,08; 50,23</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>37,51; 44,38</t>
+          <t>38,94; 45,67</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>93,06; 96,13</t>
+          <t>93,2; 96,2</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>38,72; 43,93</t>
+          <t>38,83; 43,63</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>44,74; 49,91</t>
+          <t>44,8; 49,78</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>39,26; 44,1</t>
+          <t>39,31; 44,27</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>93,84; 95,98</t>
+          <t>93,67; 95,82</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>95</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>16978</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>20530</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>29051</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>63721</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>15957</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>16257</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>23578</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>72563</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>16978</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>20530</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>29051</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>78882</t>
+          <t>55814</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>151445</t>
+          <t>119535</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11112; 21441</t>
+          <t>11370; 22696</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12344; 19457</t>
+          <t>15151; 25461</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17995; 28700</t>
+          <t>22628; 35292</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>69592; 73282</t>
+          <t>61933; 64145</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>12176; 22974</t>
+          <t>11396; 21097</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15421; 25320</t>
+          <t>12152; 19638</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23259; 34806</t>
+          <t>17480; 28864</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>76848; 79366</t>
+          <t>52417; 56481</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>25806; 41313</t>
+          <t>26408; 41340</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>30258; 42831</t>
+          <t>30034; 43464</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>44640; 61295</t>
+          <t>44323; 60786</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>147814; 152648</t>
+          <t>117019; 120626</t>
         </is>
       </c>
     </row>
@@ -2281,42 +2281,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>140</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>31469</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>26189</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>36535</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>108507</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>27413</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>23768</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>38653</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>126413</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>31469</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>26189</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>36535</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>119098</t>
+          <t>100169</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>245511</t>
+          <t>208677</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20981; 33962</t>
+          <t>25429; 38565</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17730; 29659</t>
+          <t>20442; 32101</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31559; 45867</t>
+          <t>29775; 43506</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>122864; 127654</t>
+          <t>101152; 112089</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24687; 37235</t>
+          <t>21348; 34689</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19989; 32299</t>
+          <t>17856; 29813</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29500; 43971</t>
+          <t>30468; 45130</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>111407; 123332</t>
+          <t>96703; 101395</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>49590; 69347</t>
+          <t>49992; 67865</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>40575; 58354</t>
+          <t>41236; 58081</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>66081; 85126</t>
+          <t>64453; 84963</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>237958; 250132</t>
+          <t>202134; 212942</t>
         </is>
       </c>
     </row>
@@ -2489,42 +2489,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>93</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,42 +2557,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>23121</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>27006</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>25229</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>58754</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>24690</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>26095</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>22271</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>55688</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>23121</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>27006</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>25229</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>66484</t>
+          <t>54006</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>122172</t>
+          <t>112761</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18091; 31524</t>
+          <t>17156; 29309</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20108; 32196</t>
+          <t>20909; 33019</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16142; 28831</t>
+          <t>19322; 32626</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>52519; 57625</t>
+          <t>55912; 59377</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>17172; 29759</t>
+          <t>18394; 31797</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21432; 33598</t>
+          <t>19791; 32096</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18847; 31400</t>
+          <t>15485; 28677</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>63450; 67163</t>
+          <t>50479; 55854</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>39110; 56934</t>
+          <t>39226; 56987</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>43719; 62046</t>
+          <t>44023; 62390</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>37699; 56814</t>
+          <t>38993; 57429</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>118298; 124216</t>
+          <t>108803; 114692</t>
         </is>
       </c>
     </row>
@@ -2697,42 +2697,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>88</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2765,42 +2765,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>38253</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>27715</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>24368</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>68131</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>31220</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>24041</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>26377</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>66706</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>38253</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>27715</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>24368</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>73584</t>
+          <t>67721</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>140292</t>
+          <t>135851</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>24778; 37314</t>
+          <t>31027; 44917</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18162; 30085</t>
+          <t>20902; 34266</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20569; 31500</t>
+          <t>18379; 30255</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>61753; 68881</t>
+          <t>61355; 71300</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>31062; 45179</t>
+          <t>24794; 37594</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20790; 34112</t>
+          <t>18027; 29913</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18427; 30627</t>
+          <t>19883; 31582</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>66085; 76740</t>
+          <t>62667; 69690</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>60455; 78841</t>
+          <t>60350; 78844</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>43129; 61985</t>
+          <t>43029; 60735</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>42300; 58539</t>
+          <t>42137; 58590</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>132856; 144578</t>
+          <t>128460; 139955</t>
         </is>
       </c>
     </row>
@@ -2905,42 +2905,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>68</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2973,42 +2973,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>3727</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>12547</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>14229</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>38277</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>6251</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>9834</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>15109</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>3727</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>12547</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>14229</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>38455</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>72968</t>
+          <t>73885</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3574; 8302</t>
+          <t>1377; 6724</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6199; 13511</t>
+          <t>8397; 16799</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11033; 19837</t>
+          <t>10082; 19010</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
+          <t>35228; 39579</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3550; 8279</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>6091; 13479</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>10644; 19501</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>1449; 7240</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>7960; 16484</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>9763; 19360</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>32739; 40719</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5980; 13701</t>
+          <t>6444; 13533</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16298; 27697</t>
+          <t>16758; 28198</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22853; 36181</t>
+          <t>22463; 36017</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>66971; 75232</t>
+          <t>70544; 75187</t>
         </is>
       </c>
     </row>
@@ -3113,42 +3113,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>73</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>22221</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>29223</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>9922</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>46258</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>16892</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>23454</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>10976</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>42493</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>22221</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>29223</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>9922</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>53306</t>
+          <t>42572</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>95798</t>
+          <t>88830</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>11398; 22390</t>
+          <t>16291; 27349</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>17496; 29002</t>
+          <t>23255; 34916</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7337; 15631</t>
+          <t>5682; 14527</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>38736; 44794</t>
+          <t>43206; 47962</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>16926; 27500</t>
+          <t>11821; 22532</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23292; 35030</t>
+          <t>17566; 28852</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6017; 15103</t>
+          <t>7104; 15406</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>49882; 55097</t>
+          <t>38479; 44476</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>31405; 46776</t>
+          <t>31505; 47229</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>44884; 60414</t>
+          <t>44509; 60810</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15674; 27338</t>
+          <t>15093; 27429</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>90719; 98850</t>
+          <t>84510; 91743</t>
         </is>
       </c>
     </row>
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>167</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>46000</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>65966</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>40750</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>134400</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>39978</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>62810</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>36141</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>118612</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>46000</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>65966</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>40750</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>148939</t>
+          <t>116390</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>267551</t>
+          <t>250791</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>32248; 48809</t>
+          <t>37528; 55348</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>53599; 71839</t>
+          <t>56837; 75525</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>28257; 45175</t>
+          <t>32014; 49218</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>113999; 121610</t>
+          <t>127807; 137940</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>38220; 53763</t>
+          <t>32372; 48672</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>56918; 75271</t>
+          <t>54462; 72103</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>32538; 50844</t>
+          <t>27770; 44001</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>143244; 153043</t>
+          <t>111493; 119674</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>74439; 97666</t>
+          <t>74389; 97950</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>115138; 140695</t>
+          <t>115132; 141457</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>65596; 88743</t>
+          <t>64715; 88435</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>260160; 272901</t>
+          <t>242860; 255850</t>
         </is>
       </c>
     </row>
@@ -3529,42 +3529,42 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>54</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>169</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,42 +3597,42 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>44463</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>49897</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>54536</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>146149</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>37744</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>36135</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>49569</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>116678</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>44463</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>49897</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>54536</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>143420</t>
+          <t>125197</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>260097</t>
+          <t>271347</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>30775; 45239</t>
+          <t>36295; 52563</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>28628; 44874</t>
+          <t>41461; 60320</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>41132; 58115</t>
+          <t>45473; 63726</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>108963; 122317</t>
+          <t>138501; 151749</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>37200; 52240</t>
+          <t>30576; 45337</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>41164; 59033</t>
+          <t>28243; 43751</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>46587; 65097</t>
+          <t>41764; 58874</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>136125; 148443</t>
+          <t>117498; 130822</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>71628; 93125</t>
+          <t>71572; 93576</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>74482; 98492</t>
+          <t>74087; 98121</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>93057; 117378</t>
+          <t>91878; 117319</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>249002; 267589</t>
+          <t>261225; 279706</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>925</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>296</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>320</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>330</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>893</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>226233</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>259073</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>234618</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>664197</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>200145</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>222394</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>222674</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>633667</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>226233</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>259073</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>234618</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>722169</t>
+          <t>597478</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1355836</t>
+          <t>1261676</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>181145; 217000</t>
+          <t>208384; 245623</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>204644; 239956</t>
+          <t>238688; 276489</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>206228; 241106</t>
+          <t>216293; 255101</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>624388; 642736</t>
+          <t>651951; 673502</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>208778; 245146</t>
+          <t>181684; 218077</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>240217; 278303</t>
+          <t>205485; 239569</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>214222; 253416</t>
+          <t>204609; 239933</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>709120; 732502</t>
+          <t>586887; 605754</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>399580; 453282</t>
+          <t>400649; 450187</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>454476; 506927</t>
+          <t>455074; 505661</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>430455; 483498</t>
+          <t>431014; 485340</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1340125; 1370764</t>
+          <t>1246306; 1274903</t>
         </is>
       </c>
     </row>
